--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,28 +37,97 @@
     <t>url</t>
   </si>
   <si>
+    <t>footer.report.json</t>
+  </si>
+  <si>
+    <t>["footer-cta","footer-links","footer-bottom"]</t>
+  </si>
+  <si>
+    <t>footer</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-05-11T21:56:55.987Z</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/</t>
+  </si>
+  <si>
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["announcement-bar","hero","marquee","promo-cards-semrush-one","promo-cards-enterprise","solutions-slider","stats","ai-visibility-index","testimonials","resources-slider"]</t>
+    <t>["announcement-bar","hero","marquee","promo-cards-semrush-one","promo-cards-enterprise","solutions-slider","stats-facts","stats-visibility","testimonials","resources-slider"]</t>
   </si>
   <si>
     <t>index</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-11T21:56:21.453Z</t>
+    <t>2026-05-14T20:45:16.074Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>
   </si>
   <si>
-    <t>https://www.semrush.com/</t>
+    <t>nav.report.json</t>
+  </si>
+  <si>
+    <t>["nav"]</t>
+  </si>
+  <si>
+    <t>nav</t>
+  </si>
+  <si>
+    <t>2026-05-11T21:56:38.432Z</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>one.report.json</t>
+  </si>
+  <si>
+    <t>["video-card-semrush-one","video-card-feature","video-card-feature","video-card-feature","video-card-feature","video-card-feature","video-card-feature","video-card-feature","video-card-feature","video-card-feature","video-card-feature","video-card-feature","columns-stats","cards-icon","testimonials","cards-awards"]</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
+    <t>semrush-one</t>
+  </si>
+  <si>
+    <t>2026-05-13T05:48:23.805Z</t>
+  </si>
+  <si>
+    <t>Win Every Search, From SEO to AI Discovery</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/one/</t>
+  </si>
+  <si>
+    <t>enterprise/index.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>enterprise/index</t>
+  </si>
+  <si>
+    <t>2026-05-13T09:34:40.428Z</t>
+  </si>
+  <si>
+    <t>Semrush Enterprise - The AI launchpad for elevated digital marketing</t>
+  </si>
+  <si>
+    <t>https://enterprise.semrush.com/</t>
   </si>
 </sst>
 </file>
@@ -447,16 +516,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="7" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -499,16 +568,120 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -70,7 +70,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-05-14T20:45:16.074Z</t>
+    <t>2026-06-16T13:16:06.032Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="100">
   <si>
     <t>_reportFile</t>
   </si>
@@ -19,6 +19,12 @@
     <t>blocks</t>
   </si>
   <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>errorStack</t>
+  </si>
+  <si>
     <t>path</t>
   </si>
   <si>
@@ -37,6 +43,75 @@
     <t>url</t>
   </si>
   <si>
+    <t>advertising.report.json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>advertising</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>toolkit-v2</t>
+  </si>
+  <si>
+    <t>2026-06-16T13:57:45.090Z</t>
+  </si>
+  <si>
+    <t>Advertising Toolkit Landing</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/advertising/</t>
+  </si>
+  <si>
+    <t>company.report.json</t>
+  </si>
+  <si>
+    <t>company</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:43:27.023Z</t>
+  </si>
+  <si>
+    <t>About us</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/company/</t>
+  </si>
+  <si>
+    <t>content.report.json</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:40:40.397Z</t>
+  </si>
+  <si>
+    <t>Get Your Content Seen Everywhere | Semrush Content Toolkit</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/content/</t>
+  </si>
+  <si>
+    <t>features.report.json</t>
+  </si>
+  <si>
+    <t>features</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:30:02.459Z</t>
+  </si>
+  <si>
+    <t>Features | Semrush</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/features/</t>
+  </si>
+  <si>
     <t>footer.report.json</t>
   </si>
   <si>
@@ -46,9 +121,6 @@
     <t>footer</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>2026-05-11T21:56:55.987Z</t>
   </si>
   <si>
@@ -70,7 +142,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-16T13:16:06.032Z</t>
+    <t>2026-06-17T06:21:41.440Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>
@@ -112,12 +184,110 @@
     <t>https://www.semrush.com/one/</t>
   </si>
   <si>
+    <t>pr-toolkit.report.json</t>
+  </si>
+  <si>
+    <t>pr-toolkit</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:45:21.299Z</t>
+  </si>
+  <si>
+    <t>AI PR Toolkit</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/pr-toolkit/</t>
+  </si>
+  <si>
+    <t>pricing.report.json</t>
+  </si>
+  <si>
+    <t>pricing</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:42:03.131Z</t>
+  </si>
+  <si>
+    <t>SEO Toolkit Plans and Pricing | Semrush</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/pricing/</t>
+  </si>
+  <si>
+    <t>seo.report.json</t>
+  </si>
+  <si>
+    <t>seo</t>
+  </si>
+  <si>
+    <t>toolkit</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:16:30.191Z</t>
+  </si>
+  <si>
+    <t>Semrush SEO Toolkit: Check Website SEO with Analysis Tools</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/seo/</t>
+  </si>
+  <si>
+    <t>social-media.report.json</t>
+  </si>
+  <si>
+    <t>social-media</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:43:14.826Z</t>
+  </si>
+  <si>
+    <t>Semrush Social Media Toolkit: Plan, Post &amp; Analyze From A Single Tab</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/social-media/</t>
+  </si>
+  <si>
+    <t>ai-seo/overview.report.json</t>
+  </si>
+  <si>
+    <t>page.evaluate: Target page, context or browser has been closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.evaluate: Target page, context or browser has been closed
+    at processUrl (/home/node/.excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:430:16)
+    at async main (/home/node/.excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:600:22)</t>
+  </si>
+  <si>
+    <t>ai-seo/overview</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:32:04.212Z</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/ai-seo/overview/</t>
+  </si>
+  <si>
+    <t>analytics/traffic.report.json</t>
+  </si>
+  <si>
+    <t>analytics/traffic</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:11:16.480Z</t>
+  </si>
+  <si>
+    <t>Dashboards</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/analytics/traffic/</t>
+  </si>
+  <si>
     <t>enterprise/index.report.json</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>enterprise/index</t>
   </si>
   <si>
@@ -128,6 +298,21 @@
   </si>
   <si>
     <t>https://enterprise.semrush.com/</t>
+  </si>
+  <si>
+    <t>local-business/start.report.json</t>
+  </si>
+  <si>
+    <t>local-business/start</t>
+  </si>
+  <si>
+    <t>2026-06-16T14:44:28.276Z</t>
+  </si>
+  <si>
+    <t>Local Business Tools | Drive more foot traffic with Semrush Local</t>
+  </si>
+  <si>
+    <t>https://www.semrush.com/local-business/start/</t>
   </si>
 </sst>
 </file>
@@ -516,19 +701,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -553,94 +738,118 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -649,16 +858,22 @@
         <v>29</v>
       </c>
       <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -666,26 +881,384 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
       <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>37</v>
       </c>
-      <c r="H6" t="s">
+      <c r="J6" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" t="s">
+        <v>76</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" t="s">
+        <v>88</v>
+      </c>
+      <c r="J15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" t="s">
+        <v>98</v>
+      </c>
+      <c r="J17" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
